--- a/game_config/Datas/QuestObjectiveConfig.xlsx
+++ b/game_config/Datas/QuestObjectiveConfig.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -142,10 +142,15 @@
   </si>
   <si>
     <t>击败5只怪A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>击败5只怪B</t>
+  </si>
+  <si>
+    <t>CollectItem</t>
+  </si>
+  <si>
+    <t>收集5个怪物徽记</t>
   </si>
 </sst>
 </file>
@@ -406,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -625,6 +630,29 @@
         <v>39</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>5106</v>
+      </c>
+      <c r="C10">
+        <v>5006</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>1101</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
